--- a/src/matlab/Matlab v.1.0/prior_apptest.xlsx
+++ b/src/matlab/Matlab v.1.0/prior_apptest.xlsx
@@ -1,39 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Geology1" sheetId="2" r:id="rId3"/>
-    <sheet name="Geology2" sheetId="3" r:id="rId5"/>
-    <sheet name="Resistivity" sheetId="4" r:id="rId6"/>
+    <sheet name="Geology1" sheetId="1" r:id="rId2"/>
+    <sheet name="Geology2" sheetId="2" r:id="rId4"/>
+    <sheet name="Resistivity" sheetId="3" r:id="rId5"/>
+    <sheet name="Water table" sheetId="4" r:id="rId6"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33" uniqueCount="28">
   <si>
     <t>Class</t>
   </si>
   <si>
-    <t>Meltwater deposits</t>
+    <t>Meltwater sand</t>
   </si>
   <si>
     <t>Till</t>
   </si>
   <si>
-    <t>Miocene sand</t>
-  </si>
-  <si>
-    <t>Miocene clay</t>
-  </si>
-  <si>
-    <t>Paleogene clay</t>
+    <t>Marine clay</t>
   </si>
   <si>
     <t>Min thickness</t>
@@ -45,19 +39,13 @@
     <t>RGB color</t>
   </si>
   <si>
-    <t>255,100,0</t>
-  </si>
-  <si>
-    <t>200,175,0</t>
-  </si>
-  <si>
-    <t>153,153,229</t>
-  </si>
-  <si>
-    <t>178,204,229</t>
-  </si>
-  <si>
-    <t>178,255,154</t>
+    <t>208,231,33</t>
+  </si>
+  <si>
+    <t>233,162,25</t>
+  </si>
+  <si>
+    <t>72,140,245</t>
   </si>
   <si>
     <t>Classes</t>
@@ -69,12 +57,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>Probabilities</t>
   </si>
   <si>
@@ -102,34 +84,28 @@
     <t>Min depth</t>
   </si>
   <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>Meltwater deposits</t>
-  </si>
-  <si>
-    <t>Till</t>
-  </si>
-  <si>
-    <t>Miocene sand</t>
-  </si>
-  <si>
-    <t>Miocene clay</t>
-  </si>
-  <si>
-    <t>Paleogene clay</t>
-  </si>
-  <si>
     <t>Resistivity</t>
   </si>
   <si>
     <t>Resistivity uncertainty</t>
   </si>
+  <si>
+    <t>Unsaturated resistivity</t>
+  </si>
+  <si>
+    <t>Unsaturated resistivity uncertainty</t>
+  </si>
+  <si>
+    <t>Min depth to water table</t>
+  </si>
+  <si>
+    <t>Max depth to water table</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -167,15 +143,15 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="true"/>
+    <col min="1" max="1" width="15" customWidth="true"/>
     <col min="2" max="2" width="13.28515625" customWidth="true"/>
     <col min="3" max="3" width="13.5703125" customWidth="true"/>
-    <col min="4" max="4" width="11.28515625" customWidth="true"/>
+    <col min="4" max="4" width="10.28515625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -183,13 +159,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2">
@@ -200,10 +176,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="0">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -214,10 +190,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="0">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -225,50 +201,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" s="0">
         <v>30</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0">
-        <v>3</v>
-      </c>
-      <c r="C5" s="0">
-        <v>30</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0">
-        <v>1</v>
-      </c>
-      <c r="C6" s="0">
-        <v>100</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="true"/>
@@ -284,51 +232,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="H1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="0" t="s">
         <v>21</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C2" s="0">
         <v>1</v>
       </c>
       <c r="D2" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F2" s="0">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G2" s="0">
         <v>1</v>
@@ -342,10 +290,10 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C3" s="0">
         <v>1</v>
@@ -354,13 +302,13 @@
         <v>1</v>
       </c>
       <c r="E3" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" s="0">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G3" s="0">
-        <v>0.69999999999999996</v>
+        <v>1</v>
       </c>
       <c r="H3" s="0">
         <v>1</v>
@@ -369,91 +317,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="0">
-        <v>1</v>
-      </c>
-      <c r="D4" s="0">
-        <v>1</v>
-      </c>
-      <c r="E4" s="0">
-        <v>3</v>
-      </c>
-      <c r="F4" s="0">
-        <v>30</v>
-      </c>
-      <c r="G4" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="H4" s="0">
-        <v>1</v>
-      </c>
-      <c r="I4" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="0"/>
-      <c r="D5" s="0"/>
-      <c r="E5" s="0"/>
-      <c r="F5" s="0"/>
-      <c r="G5" s="0"/>
-      <c r="H5" s="0"/>
-      <c r="I5" s="0">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="true"/>
+    <col min="1" max="1" width="15" customWidth="true"/>
     <col min="2" max="2" width="10.28515625" customWidth="true"/>
     <col min="3" max="3" width="20.85546875" customWidth="true"/>
+    <col min="4" max="4" width="21.140625" customWidth="true"/>
+    <col min="5" max="5" width="31.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>35</v>
+        <v>23</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C2" s="0">
+        <v>2</v>
+      </c>
+      <c r="D2" s="0">
+        <v>500</v>
+      </c>
+      <c r="E2" s="0">
         <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="B3" s="0">
         <v>50</v>
@@ -461,38 +377,57 @@
       <c r="C3" s="0">
         <v>2</v>
       </c>
+      <c r="D3" s="0">
+        <v>500</v>
+      </c>
+      <c r="E3" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="C4" s="0">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="0">
-        <v>20</v>
-      </c>
-      <c r="C5" s="0">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="0">
-        <v>5</v>
-      </c>
-      <c r="C6" s="0">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D4" s="0">
+        <v>500</v>
+      </c>
+      <c r="E4" s="0">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" customWidth="true"/>
+    <col min="2" max="2" width="23.42578125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>0</v>
+      </c>
+      <c r="B2" s="0">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
